--- a/data/trans_dic/P33B_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R2-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,99; 15,32</t>
+          <t>7,82; 14,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,56; 16,27</t>
+          <t>10,53; 16,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,97; 14,84</t>
+          <t>10,21; 14,42</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,68; 13,11</t>
+          <t>6,93; 12,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,75; 17,94</t>
+          <t>12,62; 17,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,46; 14,7</t>
+          <t>10,31; 14,71</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,0; 16,83</t>
+          <t>10,2; 17,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,22; 26,51</t>
+          <t>18,98; 26,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,58; 20,61</t>
+          <t>15,77; 20,93</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,08; 21,8</t>
+          <t>11,63; 21,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,07; 21,32</t>
+          <t>17,26; 24,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,68; 19,61</t>
+          <t>15,74; 21,85</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,31; 11,65</t>
+          <t>4,92; 11,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,82; 14,49</t>
+          <t>8,3; 13,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,97; 11,94</t>
+          <t>7,31; 11,16</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,73; 19,13</t>
+          <t>11,78; 19,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,75; 32,49</t>
+          <t>23,6; 32,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,7; 24,14</t>
+          <t>18,47; 24,06</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,15; 15,69</t>
+          <t>10,36; 15,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,41; 25,85</t>
+          <t>23,01; 28,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,52; 19,77</t>
+          <t>17,52; 21,65</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,07; 21,88</t>
+          <t>17,22; 22,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27,68; 33,22</t>
+          <t>27,51; 32,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,39; 26,37</t>
+          <t>23,4; 27,31</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,24; 14,6</t>
+          <t>12,84; 15,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,31; 22,4</t>
+          <t>21,33; 23,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14,96; 18,27</t>
+          <t>17,55; 19,17</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34544</t>
+          <t>34272</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38565</t>
+          <t>42158</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73109</t>
+          <t>76430</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24877; 47707</t>
+          <t>24941; 46013</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30591; 47112</t>
+          <t>33275; 50722</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59957; 89229</t>
+          <t>64835; 91548</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>50040</t>
+          <t>50825</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>78334</t>
+          <t>82057</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128373</t>
+          <t>132882</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34607; 67981</t>
+          <t>36759; 68853</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65663; 92371</t>
+          <t>68981; 98200</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>108141; 151876</t>
+          <t>111035; 158404</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41141</t>
+          <t>42094</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78902</t>
+          <t>81378</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120043</t>
+          <t>123472</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31606; 53179</t>
+          <t>32231; 53840</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>67021; 92413</t>
+          <t>67545; 94805</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103578; 136961</t>
+          <t>105957; 140598</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>51477</t>
+          <t>59283</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>77470</t>
+          <t>87121</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>128947</t>
+          <t>146404</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37752; 68135</t>
+          <t>43385; 78474</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47892; 101426</t>
+          <t>72851; 104029</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92053; 154546</t>
+          <t>125118; 173739</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14324</t>
+          <t>15270</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23559</t>
+          <t>24474</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37883</t>
+          <t>39744</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9484; 20821</t>
+          <t>10126; 22784</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18373; 30175</t>
+          <t>18837; 30915</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30844; 46208</t>
+          <t>31602; 48254</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>41124</t>
+          <t>40827</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>71381</t>
+          <t>73171</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112505</t>
+          <t>113998</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31633; 51576</t>
+          <t>31896; 52096</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>61062; 83506</t>
+          <t>62257; 84402</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>98479; 127139</t>
+          <t>98709; 128565</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>78606</t>
+          <t>90818</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>162217</t>
+          <t>198811</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>240822</t>
+          <t>289629</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>63251; 97768</t>
+          <t>74477; 111705</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>79947; 219536</t>
+          <t>177620; 221645</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>154905; 291135</t>
+          <t>261120; 322680</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>142540</t>
+          <t>159333</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>217498</t>
+          <t>251103</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>360038</t>
+          <t>410436</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>65637; 203173</t>
+          <t>137461; 181952</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>198053; 237657</t>
+          <t>228507; 270722</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>220130; 433532</t>
+          <t>381066; 444717</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>453796</t>
+          <t>492721</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>747925</t>
+          <t>840273</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1201720</t>
+          <t>1332994</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>354325; 505079</t>
+          <t>453359; 534440</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>596729; 819588</t>
+          <t>796552; 882039</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1064786; 1300366</t>
+          <t>1274926; 1392435</t>
         </is>
       </c>
     </row>
